--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/16.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/16.xlsx
@@ -426,13 +426,13 @@
         <v>-13.99543309868788</v>
       </c>
       <c r="E2">
-        <v>-13.38052404986875</v>
+        <v>-12.74920685601554</v>
       </c>
       <c r="F2">
-        <v>4.113693084239907</v>
+        <v>1.919755390986194</v>
       </c>
       <c r="G2">
-        <v>-16.04646592959315</v>
+        <v>-14.78962868135759</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.88204600687582</v>
       </c>
       <c r="E3">
-        <v>-13.76012756495808</v>
+        <v>-12.88941511713043</v>
       </c>
       <c r="F3">
-        <v>4.335289648162803</v>
+        <v>1.951531564557583</v>
       </c>
       <c r="G3">
-        <v>-15.32265657229142</v>
+        <v>-13.85306452583687</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.6977580731108</v>
       </c>
       <c r="E4">
-        <v>-14.27312392137826</v>
+        <v>-13.52512225535398</v>
       </c>
       <c r="F4">
-        <v>4.520312134517295</v>
+        <v>2.142876150930241</v>
       </c>
       <c r="G4">
-        <v>-15.46083153514839</v>
+        <v>-13.38510291697506</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.46747943340798</v>
       </c>
       <c r="E5">
-        <v>-13.78972750207014</v>
+        <v>-13.96223944086954</v>
       </c>
       <c r="F5">
-        <v>4.798902032487602</v>
+        <v>2.403762180767917</v>
       </c>
       <c r="G5">
-        <v>-14.94081951137356</v>
+        <v>-13.37804999046217</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.20633928197222</v>
       </c>
       <c r="E6">
-        <v>-14.73497763354449</v>
+        <v>-13.28592220231181</v>
       </c>
       <c r="F6">
-        <v>4.652055686258528</v>
+        <v>2.359214238580166</v>
       </c>
       <c r="G6">
-        <v>-14.67743845941598</v>
+        <v>-12.68844399804862</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.94150605848791</v>
       </c>
       <c r="E7">
-        <v>-13.653057777004</v>
+        <v>-15.07078968842482</v>
       </c>
       <c r="F7">
-        <v>4.212721093774976</v>
+        <v>2.494537994236298</v>
       </c>
       <c r="G7">
-        <v>-14.31455801497419</v>
+        <v>-12.8370136404951</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.68706620551309</v>
       </c>
       <c r="E8">
-        <v>-15.96445278203348</v>
+        <v>-14.81759331321798</v>
       </c>
       <c r="F8">
-        <v>4.792685963496995</v>
+        <v>2.555684762441346</v>
       </c>
       <c r="G8">
-        <v>-12.60900817774711</v>
+        <v>-12.3141728749558</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.46055493869678</v>
       </c>
       <c r="E9">
-        <v>-15.87185693554643</v>
+        <v>-16.68947057658615</v>
       </c>
       <c r="F9">
-        <v>4.507344871193872</v>
+        <v>2.85410743276948</v>
       </c>
       <c r="G9">
-        <v>-12.68384647682367</v>
+        <v>-12.15220358589543</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.26986877902752</v>
       </c>
       <c r="E10">
-        <v>-16.28525513118589</v>
+        <v>-16.46488152098472</v>
       </c>
       <c r="F10">
-        <v>5.302395337052781</v>
+        <v>3.352546039442776</v>
       </c>
       <c r="G10">
-        <v>-12.80064727371319</v>
+        <v>-11.45771158497961</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.12226349086772</v>
       </c>
       <c r="E11">
-        <v>-16.18457298224939</v>
+        <v>-17.25363034331689</v>
       </c>
       <c r="F11">
-        <v>4.569747444381564</v>
+        <v>3.855698056638001</v>
       </c>
       <c r="G11">
-        <v>-12.07801014073287</v>
+        <v>-11.97232719968461</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.02075783343863</v>
       </c>
       <c r="E12">
-        <v>-17.08636391042074</v>
+        <v>-17.41566372994374</v>
       </c>
       <c r="F12">
-        <v>5.412755412658147</v>
+        <v>3.477465500519747</v>
       </c>
       <c r="G12">
-        <v>-11.45566606659247</v>
+        <v>-10.94258948582393</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.96172576708202</v>
       </c>
       <c r="E13">
-        <v>-17.15141565940153</v>
+        <v>-18.07741150317398</v>
       </c>
       <c r="F13">
-        <v>5.132300031296736</v>
+        <v>3.859599667105187</v>
       </c>
       <c r="G13">
-        <v>-11.50885607151952</v>
+        <v>-10.59498450798474</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.941773511504</v>
       </c>
       <c r="E14">
-        <v>-18.78972462428399</v>
+        <v>-18.30181366426579</v>
       </c>
       <c r="F14">
-        <v>5.895408650103697</v>
+        <v>4.308929340670917</v>
       </c>
       <c r="G14">
-        <v>-10.45096930947746</v>
+        <v>-10.72143722762761</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.94452781174466</v>
       </c>
       <c r="E15">
-        <v>-19.25987645267724</v>
+        <v>-19.23352848003252</v>
       </c>
       <c r="F15">
-        <v>6.49821823606012</v>
+        <v>4.221965673990219</v>
       </c>
       <c r="G15">
-        <v>-10.6381531697988</v>
+        <v>-10.07477537299328</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.95654030592632</v>
       </c>
       <c r="E16">
-        <v>-20.13195946024208</v>
+        <v>-19.63658102626183</v>
       </c>
       <c r="F16">
-        <v>6.321012224518443</v>
+        <v>4.423923303527545</v>
       </c>
       <c r="G16">
-        <v>-9.171316764260167</v>
+        <v>-9.634904070559562</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.95258587001331</v>
       </c>
       <c r="E17">
-        <v>-20.67326410505229</v>
+        <v>-20.41385037249217</v>
       </c>
       <c r="F17">
-        <v>6.18362583402934</v>
+        <v>4.430641363164249</v>
       </c>
       <c r="G17">
-        <v>-9.357601223069874</v>
+        <v>-9.663892473126989</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.91829454564072</v>
       </c>
       <c r="E18">
-        <v>-21.03476377197669</v>
+        <v>-21.2518396682915</v>
       </c>
       <c r="F18">
-        <v>7.050921534556005</v>
+        <v>4.733494142362553</v>
       </c>
       <c r="G18">
-        <v>-8.999409675913723</v>
+        <v>-9.34906539362923</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.83191188355131</v>
       </c>
       <c r="E19">
-        <v>-21.96640382993958</v>
+        <v>-22.09504124430349</v>
       </c>
       <c r="F19">
-        <v>6.726352275525908</v>
+        <v>5.066661855033709</v>
       </c>
       <c r="G19">
-        <v>-8.473288509795687</v>
+        <v>-8.766362865360291</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.68904712957646</v>
       </c>
       <c r="E20">
-        <v>-21.88211025289085</v>
+        <v>-23.09859830956711</v>
       </c>
       <c r="F20">
-        <v>7.634958658430185</v>
+        <v>4.962214665949524</v>
       </c>
       <c r="G20">
-        <v>-8.557072525213695</v>
+        <v>-8.063415968086153</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.48261186292462</v>
       </c>
       <c r="E21">
-        <v>-22.50580630396301</v>
+        <v>-23.33945134071657</v>
       </c>
       <c r="F21">
-        <v>7.965251936213627</v>
+        <v>5.276036686295701</v>
       </c>
       <c r="G21">
-        <v>-8.015113277033668</v>
+        <v>-8.067765468574946</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.22489146879073</v>
       </c>
       <c r="E22">
-        <v>-22.70263114185796</v>
+        <v>-23.64070867737433</v>
       </c>
       <c r="F22">
-        <v>7.526671158066623</v>
+        <v>5.203385551600573</v>
       </c>
       <c r="G22">
-        <v>-8.121305313277203</v>
+        <v>-7.444993232321601</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.92439317776182</v>
       </c>
       <c r="E23">
-        <v>-24.01102145873002</v>
+        <v>-24.82365539939127</v>
       </c>
       <c r="F23">
-        <v>7.475362081137222</v>
+        <v>5.408636769931428</v>
       </c>
       <c r="G23">
-        <v>-8.603827044723646</v>
+        <v>-7.162967547866589</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.60220997800955</v>
       </c>
       <c r="E24">
-        <v>-23.41370245278185</v>
+        <v>-24.41487557474502</v>
       </c>
       <c r="F24">
-        <v>7.880016243935169</v>
+        <v>5.392312961891862</v>
       </c>
       <c r="G24">
-        <v>-7.268206662334365</v>
+        <v>-7.035988763188612</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.26975363636593</v>
       </c>
       <c r="E25">
-        <v>-25.39352167848232</v>
+        <v>-26.16957828700581</v>
       </c>
       <c r="F25">
-        <v>7.594635389996712</v>
+        <v>5.627257838143469</v>
       </c>
       <c r="G25">
-        <v>-7.93480807878332</v>
+        <v>-7.166199649670387</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.943921146828259</v>
       </c>
       <c r="E26">
-        <v>-24.17873228523792</v>
+        <v>-25.19528890194825</v>
       </c>
       <c r="F26">
-        <v>8.417446104258238</v>
+        <v>5.628372820667637</v>
       </c>
       <c r="G26">
-        <v>-8.026911231840911</v>
+        <v>-7.0319969347088</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.632086247090482</v>
       </c>
       <c r="E27">
-        <v>-24.2022477677591</v>
+        <v>-26.08932578457614</v>
       </c>
       <c r="F27">
-        <v>6.997269834611487</v>
+        <v>5.503668735115394</v>
       </c>
       <c r="G27">
-        <v>-7.513475673691094</v>
+        <v>-6.607218346756303</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.344200334496081</v>
       </c>
       <c r="E28">
-        <v>-24.65414207916839</v>
+        <v>-27.16481231677447</v>
       </c>
       <c r="F28">
-        <v>7.621494374665082</v>
+        <v>5.521367633043607</v>
       </c>
       <c r="G28">
-        <v>-6.89600847044689</v>
+        <v>-6.10881153984523</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.083814441961836</v>
       </c>
       <c r="E29">
-        <v>-23.30474295367497</v>
+        <v>-27.05290403762696</v>
       </c>
       <c r="F29">
-        <v>7.6731927842738</v>
+        <v>5.680478787038531</v>
       </c>
       <c r="G29">
-        <v>-6.796781900772448</v>
+        <v>-5.891725516349569</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.855478496330301</v>
       </c>
       <c r="E30">
-        <v>-24.8355543498369</v>
+        <v>-27.03657776390906</v>
       </c>
       <c r="F30">
-        <v>7.736383963228957</v>
+        <v>5.548857833672912</v>
       </c>
       <c r="G30">
-        <v>-6.848090864221597</v>
+        <v>-5.822877570737321</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.662228270198824</v>
       </c>
       <c r="E31">
-        <v>-25.05770547039066</v>
+        <v>-27.61087967269503</v>
       </c>
       <c r="F31">
-        <v>7.549421440417109</v>
+        <v>5.794977386188284</v>
       </c>
       <c r="G31">
-        <v>-6.429439693824444</v>
+        <v>-5.291296032306971</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.505984571062124</v>
       </c>
       <c r="E32">
-        <v>-24.37024101263709</v>
+        <v>-27.33670127387515</v>
       </c>
       <c r="F32">
-        <v>7.696040813977816</v>
+        <v>5.492414535580959</v>
       </c>
       <c r="G32">
-        <v>-6.870485831324167</v>
+        <v>-5.154712318278289</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.389858831671814</v>
       </c>
       <c r="E33">
-        <v>-25.92909904487558</v>
+        <v>-27.71633801465508</v>
       </c>
       <c r="F33">
-        <v>7.686468200271064</v>
+        <v>5.57159983234937</v>
       </c>
       <c r="G33">
-        <v>-6.015555743050664</v>
+        <v>-5.028190413903757</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.313597512421007</v>
       </c>
       <c r="E34">
-        <v>-24.26641903593902</v>
+        <v>-27.93691922132804</v>
       </c>
       <c r="F34">
-        <v>7.41621167837292</v>
+        <v>5.568011344760443</v>
       </c>
       <c r="G34">
-        <v>-6.165548241299304</v>
+        <v>-4.576111269761989</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.280271920253796</v>
       </c>
       <c r="E35">
-        <v>-24.458833163407</v>
+        <v>-27.59390134479913</v>
       </c>
       <c r="F35">
-        <v>7.594448178963678</v>
+        <v>5.693697874052406</v>
       </c>
       <c r="G35">
-        <v>-6.5207008817514</v>
+        <v>-4.820215889031082</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.287449204831397</v>
       </c>
       <c r="E36">
-        <v>-27.08151135723238</v>
+        <v>-27.63261758076918</v>
       </c>
       <c r="F36">
-        <v>7.526818607464321</v>
+        <v>5.825994775218709</v>
       </c>
       <c r="G36">
-        <v>-6.156825743620395</v>
+        <v>-4.204926046775866</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.336177909530155</v>
       </c>
       <c r="E37">
-        <v>-23.83374163332971</v>
+        <v>-27.39062656971672</v>
       </c>
       <c r="F37">
-        <v>7.431392339396623</v>
+        <v>5.782068108583057</v>
       </c>
       <c r="G37">
-        <v>-6.175818910520744</v>
+        <v>-3.901635847626236</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.419297814059059</v>
       </c>
       <c r="E38">
-        <v>-24.57689234852658</v>
+        <v>-27.63755159582308</v>
       </c>
       <c r="F38">
-        <v>7.560122290526473</v>
+        <v>6.087835084304411</v>
       </c>
       <c r="G38">
-        <v>-6.840859101704213</v>
+        <v>-4.424954379425712</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.533938355290553</v>
       </c>
       <c r="E39">
-        <v>-23.24792286953999</v>
+        <v>-26.76735829941103</v>
       </c>
       <c r="F39">
-        <v>8.112461107365126</v>
+        <v>6.273465592332557</v>
       </c>
       <c r="G39">
-        <v>-6.09201923063519</v>
+        <v>-3.498578654671803</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.669396117350866</v>
       </c>
       <c r="E40">
-        <v>-25.19729074980682</v>
+        <v>-27.11113206040106</v>
       </c>
       <c r="F40">
-        <v>8.031314236586887</v>
+        <v>6.415186001073108</v>
       </c>
       <c r="G40">
-        <v>-6.099203999749934</v>
+        <v>-4.122979995550003</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.821802872939507</v>
       </c>
       <c r="E41">
-        <v>-24.2869566659403</v>
+        <v>-25.99328692590081</v>
       </c>
       <c r="F41">
-        <v>7.597390539978423</v>
+        <v>6.147987811626099</v>
       </c>
       <c r="G41">
-        <v>-6.709940703438247</v>
+        <v>-3.861161474230207</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.979872306855967</v>
       </c>
       <c r="E42">
-        <v>-23.22444891913207</v>
+        <v>-26.31238230519871</v>
       </c>
       <c r="F42">
-        <v>7.52049485071135</v>
+        <v>6.312465129656358</v>
       </c>
       <c r="G42">
-        <v>-6.546461098631915</v>
+        <v>-4.265769449471762</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.141264565781212</v>
       </c>
       <c r="E43">
-        <v>-23.66024953665765</v>
+        <v>-25.89927068114066</v>
       </c>
       <c r="F43">
-        <v>7.438811197856096</v>
+        <v>6.393931750252078</v>
       </c>
       <c r="G43">
-        <v>-6.598986669060523</v>
+        <v>-4.313386820069077</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.296159934169417</v>
       </c>
       <c r="E44">
-        <v>-23.15815535996515</v>
+        <v>-26.31314649608248</v>
       </c>
       <c r="F44">
-        <v>7.851624779571619</v>
+        <v>6.60455244608788</v>
       </c>
       <c r="G44">
-        <v>-6.39371426483965</v>
+        <v>-4.405561768602922</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.444789295821019</v>
       </c>
       <c r="E45">
-        <v>-22.98299782555183</v>
+        <v>-25.5163155245122</v>
       </c>
       <c r="F45">
-        <v>7.983800739097114</v>
+        <v>6.407026582155533</v>
       </c>
       <c r="G45">
-        <v>-6.314073501087739</v>
+        <v>-4.156431465995937</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.579607030646361</v>
       </c>
       <c r="E46">
-        <v>-22.880201692051</v>
+        <v>-24.71183433768158</v>
       </c>
       <c r="F46">
-        <v>7.506553427322234</v>
+        <v>6.745873581740282</v>
       </c>
       <c r="G46">
-        <v>-6.715540750586184</v>
+        <v>-4.919836681138782</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.702453070006268</v>
       </c>
       <c r="E47">
-        <v>-21.20241645352604</v>
+        <v>-24.55903353982982</v>
       </c>
       <c r="F47">
-        <v>8.027969289014383</v>
+        <v>6.558019735603021</v>
       </c>
       <c r="G47">
-        <v>-5.544932480078218</v>
+        <v>-4.591070836269068</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.806987076078462</v>
       </c>
       <c r="E48">
-        <v>-22.25300448383202</v>
+        <v>-24.54693938845192</v>
       </c>
       <c r="F48">
-        <v>7.552224635708182</v>
+        <v>6.187875358805702</v>
       </c>
       <c r="G48">
-        <v>-6.801191448386838</v>
+        <v>-5.151730847955237</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.895303743030812</v>
       </c>
       <c r="E49">
-        <v>-20.80918209886863</v>
+        <v>-24.65660908669534</v>
       </c>
       <c r="F49">
-        <v>7.533801744669921</v>
+        <v>6.337642528497046</v>
       </c>
       <c r="G49">
-        <v>-6.76730920508337</v>
+        <v>-4.535101693724782</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.96299084041936</v>
       </c>
       <c r="E50">
-        <v>-20.60123496104578</v>
+        <v>-24.50372107140575</v>
       </c>
       <c r="F50">
-        <v>7.531165879594213</v>
+        <v>6.261096410273955</v>
       </c>
       <c r="G50">
-        <v>-6.249139061617569</v>
+        <v>-4.783848216876874</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.0126191886664</v>
       </c>
       <c r="E51">
-        <v>-20.16238173319645</v>
+        <v>-24.38531301653489</v>
       </c>
       <c r="F51">
-        <v>7.69458951428811</v>
+        <v>6.382472115601749</v>
       </c>
       <c r="G51">
-        <v>-6.782226999676991</v>
+        <v>-4.980426841609339</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.0423820123852</v>
       </c>
       <c r="E52">
-        <v>-19.4000307220449</v>
+        <v>-22.84433040583846</v>
       </c>
       <c r="F52">
-        <v>7.986592337244548</v>
+        <v>6.245372340234015</v>
       </c>
       <c r="G52">
-        <v>-7.70244528331276</v>
+        <v>-5.232888454314585</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.05420879288243</v>
       </c>
       <c r="E53">
-        <v>-22.03210763309836</v>
+        <v>-23.1060408642612</v>
       </c>
       <c r="F53">
-        <v>7.447253918425429</v>
+        <v>6.223452082021135</v>
       </c>
       <c r="G53">
-        <v>-6.740807536738979</v>
+        <v>-5.130374957199931</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.04876618299148</v>
       </c>
       <c r="E54">
-        <v>-19.48077745662222</v>
+        <v>-22.99007074443801</v>
       </c>
       <c r="F54">
-        <v>7.453342418836005</v>
+        <v>6.397162383122996</v>
       </c>
       <c r="G54">
-        <v>-7.145747076543605</v>
+        <v>-4.854667274655412</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.02762924269058</v>
       </c>
       <c r="E55">
-        <v>-19.96335569329935</v>
+        <v>-23.05680454400536</v>
       </c>
       <c r="F55">
-        <v>6.983992761879416</v>
+        <v>6.136168665522956</v>
       </c>
       <c r="G55">
-        <v>-7.06007027129704</v>
+        <v>-5.325582941022063</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.994141539319758</v>
       </c>
       <c r="E56">
-        <v>-19.46754532534131</v>
+        <v>-21.33687251695604</v>
       </c>
       <c r="F56">
-        <v>7.046789637950841</v>
+        <v>6.314562555920246</v>
       </c>
       <c r="G56">
-        <v>-7.731607300395495</v>
+        <v>-5.387974515260487</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.948944289963666</v>
       </c>
       <c r="E57">
-        <v>-20.3253495923714</v>
+        <v>-22.17245710339829</v>
       </c>
       <c r="F57">
-        <v>6.95960893901061</v>
+        <v>6.485444810708951</v>
       </c>
       <c r="G57">
-        <v>-8.168326128735448</v>
+        <v>-5.165604344712413</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.897789399701034</v>
       </c>
       <c r="E58">
-        <v>-17.87841038254482</v>
+        <v>-22.14021157067232</v>
       </c>
       <c r="F58">
-        <v>7.526805353585877</v>
+        <v>6.373939931352915</v>
       </c>
       <c r="G58">
-        <v>-8.249186110211408</v>
+        <v>-5.911065912280537</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.840709681600009</v>
       </c>
       <c r="E59">
-        <v>-19.20411128421876</v>
+        <v>-21.71271322258507</v>
       </c>
       <c r="F59">
-        <v>7.203389181980477</v>
+        <v>6.023215799946827</v>
       </c>
       <c r="G59">
-        <v>-7.837818917223462</v>
+        <v>-5.69809442226047</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.785168374009983</v>
       </c>
       <c r="E60">
-        <v>-18.29027604320541</v>
+        <v>-21.62537118842393</v>
       </c>
       <c r="F60">
-        <v>7.294842599984348</v>
+        <v>6.297027674737786</v>
       </c>
       <c r="G60">
-        <v>-8.083660987017939</v>
+        <v>-6.130039504115572</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.731333849259032</v>
       </c>
       <c r="E61">
-        <v>-18.94215578632785</v>
+        <v>-21.38930265672068</v>
       </c>
       <c r="F61">
-        <v>7.247503059649161</v>
+        <v>6.849779018543035</v>
       </c>
       <c r="G61">
-        <v>-7.601113148125584</v>
+        <v>-6.193574584484906</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.688628913740462</v>
       </c>
       <c r="E62">
-        <v>-17.98806762115426</v>
+        <v>-20.99436548542008</v>
       </c>
       <c r="F62">
-        <v>6.852476182806551</v>
+        <v>6.546089588267902</v>
       </c>
       <c r="G62">
-        <v>-7.789815156426662</v>
+        <v>-6.597850995163388</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.657320507219032</v>
       </c>
       <c r="E63">
-        <v>-17.88315334987777</v>
+        <v>-21.13717781003563</v>
       </c>
       <c r="F63">
-        <v>7.152529080183393</v>
+        <v>6.280844689156695</v>
       </c>
       <c r="G63">
-        <v>-8.190619276798964</v>
+        <v>-6.571874086481811</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.64621302986337</v>
       </c>
       <c r="E64">
-        <v>-17.56912904160749</v>
+        <v>-21.03847258968976</v>
       </c>
       <c r="F64">
-        <v>7.269019074569476</v>
+        <v>6.283077967674643</v>
       </c>
       <c r="G64">
-        <v>-9.119031382333942</v>
+        <v>-6.940714860825114</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.653113214109823</v>
       </c>
       <c r="E65">
-        <v>-17.06909070452078</v>
+        <v>-20.96463264554563</v>
       </c>
       <c r="F65">
-        <v>7.007533306732173</v>
+        <v>6.201967545062127</v>
       </c>
       <c r="G65">
-        <v>-9.142650788649744</v>
+        <v>-6.837467744480358</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.683679312948488</v>
       </c>
       <c r="E66">
-        <v>-17.96713958928845</v>
+        <v>-20.998634986662</v>
       </c>
       <c r="F66">
-        <v>7.010092962006823</v>
+        <v>6.722231976064384</v>
       </c>
       <c r="G66">
-        <v>-8.302218165090693</v>
+        <v>-7.821514817251959</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.732874923488453</v>
       </c>
       <c r="E67">
-        <v>-17.97974873887063</v>
+        <v>-21.82062195922677</v>
       </c>
       <c r="F67">
-        <v>7.314030902502796</v>
+        <v>6.292703596895173</v>
       </c>
       <c r="G67">
-        <v>-8.014125110205933</v>
+        <v>-6.937608074761689</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.803135803086253</v>
       </c>
       <c r="E68">
-        <v>-17.37013622740097</v>
+        <v>-20.85755039795758</v>
       </c>
       <c r="F68">
-        <v>6.498533015673183</v>
+        <v>6.470974888916849</v>
       </c>
       <c r="G68">
-        <v>-9.04675030758438</v>
+        <v>-7.280986257107864</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.887990619440391</v>
       </c>
       <c r="E69">
-        <v>-16.61906118499633</v>
+        <v>-20.6680975101642</v>
       </c>
       <c r="F69">
-        <v>6.95591607712893</v>
+        <v>6.702967463744878</v>
       </c>
       <c r="G69">
-        <v>-8.785793331979651</v>
+        <v>-7.328648010363229</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.987280387643926</v>
       </c>
       <c r="E70">
-        <v>-17.09182538331289</v>
+        <v>-19.62500602629954</v>
       </c>
       <c r="F70">
-        <v>7.301037131422483</v>
+        <v>6.606038537208502</v>
       </c>
       <c r="G70">
-        <v>-8.879067403986356</v>
+        <v>-7.613670829608839</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.09349150232721</v>
       </c>
       <c r="E71">
-        <v>-16.93233376201682</v>
+        <v>-19.71750219571479</v>
       </c>
       <c r="F71">
-        <v>6.887002536155234</v>
+        <v>6.661161417660393</v>
       </c>
       <c r="G71">
-        <v>-8.811604458379692</v>
+        <v>-8.092386095441441</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.20255994927831</v>
       </c>
       <c r="E72">
-        <v>-19.32954241943991</v>
+        <v>-20.57471255352543</v>
       </c>
       <c r="F72">
-        <v>7.21433522884107</v>
+        <v>6.560098937784048</v>
       </c>
       <c r="G72">
-        <v>-8.598250494277028</v>
+        <v>-8.263205808665687</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.3060478779827</v>
       </c>
       <c r="E73">
-        <v>-19.01329198989951</v>
+        <v>-21.21366334979368</v>
       </c>
       <c r="F73">
-        <v>6.467194220090472</v>
+        <v>6.826932645573825</v>
       </c>
       <c r="G73">
-        <v>-8.741978510879292</v>
+        <v>-8.025896957567262</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.39795833684659</v>
       </c>
       <c r="E74">
-        <v>-17.97815805893323</v>
+        <v>-19.31008047117176</v>
       </c>
       <c r="F74">
-        <v>7.09882270799029</v>
+        <v>6.787676314355156</v>
       </c>
       <c r="G74">
-        <v>-9.131478107172075</v>
+        <v>-8.279562123529011</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.47342016276465</v>
       </c>
       <c r="E75">
-        <v>-17.49411373865843</v>
+        <v>-19.72883215620892</v>
       </c>
       <c r="F75">
-        <v>6.854538817639521</v>
+        <v>6.565562849172913</v>
       </c>
       <c r="G75">
-        <v>-7.919665760154863</v>
+        <v>-8.635505819592215</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.52676481643869</v>
       </c>
       <c r="E76">
-        <v>-19.21078134160644</v>
+        <v>-20.50186107367661</v>
       </c>
       <c r="F76">
-        <v>6.843685547928041</v>
+        <v>6.941244033690545</v>
       </c>
       <c r="G76">
-        <v>-9.431874295942457</v>
+        <v>-8.584088510242534</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.55654948079809</v>
       </c>
       <c r="E77">
-        <v>-18.90187794289966</v>
+        <v>-21.18530106965642</v>
       </c>
       <c r="F77">
-        <v>6.765280573253069</v>
+        <v>7.034831326124028</v>
       </c>
       <c r="G77">
-        <v>-9.024941452642516</v>
+        <v>-8.34496388628099</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.55697750507692</v>
       </c>
       <c r="E78">
-        <v>-18.21133180234307</v>
+        <v>-21.21874272724394</v>
       </c>
       <c r="F78">
-        <v>6.371743101000691</v>
+        <v>6.739266523335553</v>
       </c>
       <c r="G78">
-        <v>-8.882043652820224</v>
+        <v>-8.164535327589151</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.52923316291111</v>
       </c>
       <c r="E79">
-        <v>-18.94085167797186</v>
+        <v>-21.43514165011281</v>
       </c>
       <c r="F79">
-        <v>6.47157297018167</v>
+        <v>6.777484081831111</v>
       </c>
       <c r="G79">
-        <v>-7.587581658909844</v>
+        <v>-8.297518824826689</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.46703705343342</v>
       </c>
       <c r="E80">
-        <v>-20.03963357249114</v>
+        <v>-20.9708832285895</v>
       </c>
       <c r="F80">
-        <v>7.039919158712022</v>
+        <v>6.588669329506603</v>
       </c>
       <c r="G80">
-        <v>-8.15822254716784</v>
+        <v>-8.362889258643575</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.37247623062828</v>
       </c>
       <c r="E81">
-        <v>-20.500370070811</v>
+        <v>-21.68855814551987</v>
       </c>
       <c r="F81">
-        <v>7.037684223459269</v>
+        <v>6.788206469492947</v>
       </c>
       <c r="G81">
-        <v>-8.004107683209831</v>
+        <v>-8.007924591802039</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.2390572500461</v>
       </c>
       <c r="E82">
-        <v>-21.33930629879239</v>
+        <v>-22.84543516005086</v>
       </c>
       <c r="F82">
-        <v>6.740255594014496</v>
+        <v>6.696048939196698</v>
       </c>
       <c r="G82">
-        <v>-8.206174093072818</v>
+        <v>-7.696097257839468</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.06972389385723</v>
       </c>
       <c r="E83">
-        <v>-21.84201515076096</v>
+        <v>-24.25529673601113</v>
       </c>
       <c r="F83">
-        <v>6.621018733320729</v>
+        <v>7.139407740523048</v>
       </c>
       <c r="G83">
-        <v>-7.648623478194664</v>
+        <v>-8.119066599790322</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.85955465093042</v>
       </c>
       <c r="E84">
-        <v>-23.37943845935202</v>
+        <v>-24.43400526610718</v>
       </c>
       <c r="F84">
-        <v>6.753878924320937</v>
+        <v>6.621706278265052</v>
       </c>
       <c r="G84">
-        <v>-7.778662055533426</v>
+        <v>-7.410933458385937</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.613234120547586</v>
       </c>
       <c r="E85">
-        <v>-22.26894866210803</v>
+        <v>-25.76418332958929</v>
       </c>
       <c r="F85">
-        <v>6.462099760563255</v>
+        <v>6.892420058969543</v>
       </c>
       <c r="G85">
-        <v>-8.517829117892374</v>
+        <v>-8.004491462664724</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.330671101627638</v>
       </c>
       <c r="E86">
-        <v>-26.18053030526938</v>
+        <v>-26.82746772691527</v>
       </c>
       <c r="F86">
-        <v>6.661038819284779</v>
+        <v>7.421387317905611</v>
       </c>
       <c r="G86">
-        <v>-7.123542693796186</v>
+        <v>-7.325199216758368</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.019878063248589</v>
       </c>
       <c r="E87">
-        <v>-26.07838207273522</v>
+        <v>-28.05031019691851</v>
       </c>
       <c r="F87">
-        <v>6.895307747735702</v>
+        <v>6.82028251206415</v>
       </c>
       <c r="G87">
-        <v>-7.917997494361142</v>
+        <v>-7.461373043886246</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.686473976030165</v>
       </c>
       <c r="E88">
-        <v>-27.15237344885661</v>
+        <v>-28.58962337689846</v>
       </c>
       <c r="F88">
-        <v>7.523564780306125</v>
+        <v>7.565150480661465</v>
       </c>
       <c r="G88">
-        <v>-7.410476578082492</v>
+        <v>-7.211579612153118</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.340105852546172</v>
       </c>
       <c r="E89">
-        <v>-27.89568198608382</v>
+        <v>-30.21470644031701</v>
       </c>
       <c r="F89">
-        <v>6.600756866648253</v>
+        <v>7.258990858791186</v>
       </c>
       <c r="G89">
-        <v>-6.434812606192955</v>
+        <v>-6.945518630872763</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.989940005773692</v>
       </c>
       <c r="E90">
-        <v>-32.66048275097264</v>
+        <v>-31.24108747841622</v>
       </c>
       <c r="F90">
-        <v>6.887632095381361</v>
+        <v>7.41366693371152</v>
       </c>
       <c r="G90">
-        <v>-6.023902293508453</v>
+        <v>-6.471096734520247</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.642755508873821</v>
       </c>
       <c r="E91">
-        <v>-31.47464539387362</v>
+        <v>-32.70859147435379</v>
       </c>
       <c r="F91">
-        <v>7.117871844785067</v>
+        <v>7.313465955934086</v>
       </c>
       <c r="G91">
-        <v>-6.693315481882038</v>
+        <v>-5.932630662603133</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.30668093934891</v>
       </c>
       <c r="E92">
-        <v>-33.67364827063625</v>
+        <v>-34.86971498722832</v>
       </c>
       <c r="F92">
-        <v>6.987119020457582</v>
+        <v>7.381325813571422</v>
       </c>
       <c r="G92">
-        <v>-6.718383851445907</v>
+        <v>-6.217196601545298</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.98184726076245</v>
       </c>
       <c r="E93">
-        <v>-35.81225722491889</v>
+        <v>-36.65052063266565</v>
       </c>
       <c r="F93">
-        <v>7.067208894429849</v>
+        <v>7.650124408840639</v>
       </c>
       <c r="G93">
-        <v>-6.080732981767807</v>
+        <v>-6.332568015771185</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.673318744212139</v>
       </c>
       <c r="E94">
-        <v>-36.8120244848486</v>
+        <v>-38.3374450127109</v>
       </c>
       <c r="F94">
-        <v>6.680296704665062</v>
+        <v>7.342036347656641</v>
       </c>
       <c r="G94">
-        <v>-6.338609278755022</v>
+        <v>-5.983913518606371</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.376612988214688</v>
       </c>
       <c r="E95">
-        <v>-38.7531669300866</v>
+        <v>-40.75352586239401</v>
       </c>
       <c r="F95">
-        <v>7.228016544865706</v>
+        <v>7.525947164956576</v>
       </c>
       <c r="G95">
-        <v>-5.249662488312488</v>
+        <v>-5.963105884215198</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.098293072992442</v>
       </c>
       <c r="E96">
-        <v>-42.21460899362339</v>
+        <v>-42.48287529612237</v>
       </c>
       <c r="F96">
-        <v>6.400624958866699</v>
+        <v>7.851053206063687</v>
       </c>
       <c r="G96">
-        <v>-5.697851623013497</v>
+        <v>-5.250189858719893</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.835306264779636</v>
       </c>
       <c r="E97">
-        <v>-44.5511018546888</v>
+        <v>-45.49241889503855</v>
       </c>
       <c r="F97">
-        <v>6.180938610174658</v>
+        <v>7.446022964464869</v>
       </c>
       <c r="G97">
-        <v>-5.302885127546923</v>
+        <v>-5.566711311457285</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.601179223062029</v>
       </c>
       <c r="E98">
-        <v>-45.9440692052825</v>
+        <v>-47.49518668991435</v>
       </c>
       <c r="F98">
-        <v>5.998492346442872</v>
+        <v>7.606457849569466</v>
       </c>
       <c r="G98">
-        <v>-5.023634664592264</v>
+        <v>-5.40927296963479</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.396071669725529</v>
       </c>
       <c r="E99">
-        <v>-49.63819908650414</v>
+        <v>-49.194122157111</v>
       </c>
       <c r="F99">
-        <v>6.021451377378864</v>
+        <v>7.548220307683049</v>
       </c>
       <c r="G99">
-        <v>-5.406727493658455</v>
+        <v>-5.544987305714632</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.242174865236138</v>
       </c>
       <c r="E100">
-        <v>-50.85212357349014</v>
+        <v>-51.76331944870656</v>
       </c>
       <c r="F100">
-        <v>6.310112566232408</v>
+        <v>7.269822590950191</v>
       </c>
       <c r="G100">
-        <v>-5.064346615746085</v>
+        <v>-4.704465916839482</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.135413147265949</v>
       </c>
       <c r="E101">
-        <v>-53.45852014061936</v>
+        <v>-53.43507941590202</v>
       </c>
       <c r="F101">
-        <v>5.020273280476936</v>
+        <v>7.373197872615153</v>
       </c>
       <c r="G101">
-        <v>-5.829234733816682</v>
+        <v>-4.937662845206904</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.109580438500328</v>
       </c>
       <c r="E102">
-        <v>-54.5199833547794</v>
+        <v>-55.68985161433445</v>
       </c>
       <c r="F102">
-        <v>5.195113474716217</v>
+        <v>7.363300538886504</v>
       </c>
       <c r="G102">
-        <v>-6.091050644391887</v>
+        <v>-4.755098697439534</v>
       </c>
     </row>
   </sheetData>
